--- a/docentes/Castro Vasquez Julieta - Estadisticos 20241.xlsx
+++ b/docentes/Castro Vasquez Julieta - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="18">
   <si>
     <t>Mat</t>
   </si>
@@ -47,9 +47,6 @@
   </si>
   <si>
     <t>3AEM</t>
-  </si>
-  <si>
-    <t>3APM</t>
   </si>
   <si>
     <t>3BEM</t>
@@ -431,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -497,7 +494,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -506,13 +503,13 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>96.43000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -523,47 +520,21 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G4">
-        <v>95.83</v>
+        <v>94.59</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5">
-        <v>37</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>35</v>
-      </c>
-      <c r="G5">
-        <v>94.59</v>
-      </c>
-      <c r="H5">
         <v>8.300000000000001</v>
       </c>
     </row>
@@ -574,7 +545,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -617,16 +588,19 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -637,19 +611,22 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -660,42 +637,22 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5">
-        <v>37</v>
-      </c>
-      <c r="D5">
-        <v>37</v>
-      </c>
-      <c r="E5">
-        <v>37</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -705,7 +662,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -751,16 +708,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -771,22 +728,22 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>96.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -797,48 +754,22 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="G4">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5">
-        <v>37</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>35</v>
-      </c>
-      <c r="G5">
-        <v>94.59</v>
-      </c>
-      <c r="H5">
-        <v>8.300000000000001</v>
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>
@@ -857,25 +788,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
